--- a/artfynd/A 46640-2024 artfynd.xlsx
+++ b/artfynd/A 46640-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122649193</v>
       </c>
       <c r="B2" t="n">
-        <v>97194</v>
+        <v>97195</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 46640-2024 artfynd.xlsx
+++ b/artfynd/A 46640-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122649193</v>
       </c>
       <c r="B2" t="n">
-        <v>97195</v>
+        <v>97198</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 46640-2024 artfynd.xlsx
+++ b/artfynd/A 46640-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122649193</v>
       </c>
       <c r="B2" t="n">
-        <v>97198</v>
+        <v>97301</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 46640-2024 artfynd.xlsx
+++ b/artfynd/A 46640-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122649193</v>
       </c>
       <c r="B2" t="n">
-        <v>97301</v>
+        <v>97309</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 46640-2024 artfynd.xlsx
+++ b/artfynd/A 46640-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122649193</v>
       </c>
       <c r="B2" t="n">
-        <v>97309</v>
+        <v>97311</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 46640-2024 artfynd.xlsx
+++ b/artfynd/A 46640-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122649193</v>
       </c>
       <c r="B2" t="n">
-        <v>97311</v>
+        <v>97319</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
